--- a/experiments/rq1-3-4-5/summary/visidroid_evals.xlsx
+++ b/experiments/rq1-3-4-5/summary/visidroid_evals.xlsx
@@ -1,42 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minhh\OneDrive\Documents\mobile-testing\summary\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE710A23-1941-4D86-98AA-30D3BFDA58EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$151</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="631">
   <si>
     <t>app_name</t>
   </si>
@@ -1035,23 +1013,22 @@
 - action 11: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "settings"
-- action 4: touched on a button that has text "display events from the past, 1 day"
-- action 10: touched on a button that has content-desc "back"
-- action 11: touched on a button that has content-desc "more options"
-- action 12: touched on a button that has text "add holidays"
-- action 14: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "settings"
-- action 3: touched on a button that has text "caldav sync"
-- action 4: touched on a button that has text "allow"
-- action 5: touched on a button that has text "cancel"
-- action 7: touched on a button that has content-desc "back"
-- action 8: touched on a button that has content-desc "more options"
-- action 9: touched on a button that has text "add holidays"
-- action 13: touched on a button that has text "united states"
-- action 14: task completed?</t>
+    <t>- action 1: jade green touched on a button that has text "holidays"
+- action 2: jade green long touched on a button that has content_desc "more options"
+- action 3: jade green touched on a button that has content_desc "filter events by type"
+- action 4: jade green touched on a button that has text "ok"
+- action 5: jade green touched on a button that has content_desc "more options"
+- action 6: jade green touched on a button that has text "add holidays"
+- action 9: jade green touched on a button that has text "south africa"
+- action 10: jade green touched on a button that has text "ok"
+- action 11: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "add holidays"
+- action 6: jade green touched on a button that has text "united states"
+- action 7: jade green touched on a button that has text "ok"
+- action 8: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "settings"
@@ -1059,34 +1036,23 @@
 - action 3: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "new event"
-- action 2: touched on a button that has text "event"
-- action 3: filled a focused textfield that has text "title" with the text "john doe's birthday"
-- action 4: touched on a button that has text "september 10 (tue)"
-- action 5: touched on a button that has text "ok"
-- action 6: touched on a button that has content-desc "save"
-- action 7: touched on a button that has content-desc "new event"
-- action 8: touched on a button that has text "event"
-- action 9: filled a focused textfield that has text "title" with the text "jane smith's birthday"
-- action 10: touched on a button that has text "september 10 (tue)"
-- action 11: touched on a button that has text "ok"
-- action 12: touched on a button that has content-desc "save"
-- action 13: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "new event"
-- action 2: touched on a button that has content-desc "new event"
-- action 3: filled a focused textfield that has text "title" with the text "john's anniversary"
-- action 4: touched on a button that has text "september 10 (tue)"
-- action 5: touched on a button that has text "ok"
-- action 6: touched on a button that has content-desc "save"
-- action 7: touched on a button that has content-desc "new event"
-- action 8: touched on a button that has text "event"
-- action 9: filled a focused textfield that has text "title" with the text "sarah's anniversary"
-- action 10: touched on a button that has text "september 10 (tue)"
-- action 11: touched on a button that has text "ok"
-- action 12: touched on a button that has content-desc "save"
-- action 13: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "add contact birthdays"
+- action 3: jade green touched on a button that has text "ok"
+- action 4: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has text "anniversaries"
+- action 2: jade green touched on a button that has content_desc "new event"
+- action 3: jade green touched on a button that has text "event"
+- action 4: jade green filled a focused textfield that has text "title" with the text "john doe anniversary"
+- action 5: jade green touched on a button that has text "no repetition"
+- action 6: jade green touched on a button that has text "yearly"
+- action 7: jade green touched on a button that has text "february 13 (thu)"
+- action 8: jade green touched on a button that has text "ok"
+- action 9: jade green touched on a checkbox that has text "all-day"
+- action 10: jade green touched on a button that has content_desc "save"
+- action 11: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "new event"
@@ -1138,15 +1104,12 @@
 - action 5: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 3: touched on a button that has content-desc "change view"
-- action 5: touched on a button that has content-desc "more options"
-- action 7: touched on a button that has content-desc "search"
-- action 9: touched on a button that has content-desc "more options"
-- action 11: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/small_month_view"
-- action 12: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"
-- action 13: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/top_right_arrow"
-- action 14: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "new event"
+- action 2: jade green filled a focused textfield that has text "title" with the text "homework"
+- action 3: jade green touched on a button that has text "no repetition"
+- action 4: jade green touched on a button that has text "daily"
+- action 5: jade green touched on a button that has content_desc "save"
+- action 6: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "more options"
@@ -1168,16 +1131,15 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 3: touched on a button that has content-desc "settings"
-- action 7: touched on a button that has text "export events to an .ics file"
-- action 8: filled a textfield that has text "events_2024_09_10_19_07_52" with the text "dcim/test.ics"
-- action 9: touched on a button that has text "ok"
-- action 10: filled a focused textfield that has text "dcim/test.ics" with the text "test.ics"
-- action 11: touched on a button that has text "ok"
-- action 12: filled a textfield that has text "test.ics.ics" with the text "test.ics"
-- action 13: touched on a button that has text "save"
-- action 14: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "settings"
+- action 3: jade green touched on a button that has content_desc "back"
+- action 4: jade green touched on a button that has content_desc "more options"
+- action 5: jade green touched on a button that has text "print"
+- action 6: jade green touched on a button that has content_desc "save to pdf"
+- action 8: jade green touched on a button that has content_desc "more options"
+- action 10: jade green touched on a button that has content_desc "more options"
+- action 11: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "search"
@@ -1212,32 +1174,23 @@
 - action 5: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "shutter"
-- action 4: touched on a button that has content-desc "view last captured media"
-- action 6: touched on a button that has content-desc "view last captured media"
-- action 8: touched on a button that has content-desc "view last captured media"
-- action 10: touched on a button that has content-desc "view last captured media"
-- action 11: task completed?</t>
+    <t>- action 1: jade green waited for a loading state to finish
+- action 2: jade green touched on a button that has content_desc "view last captured media"
+- action 3: jade green touched on a button that has text "just once"
+- action 4: jade green touched on a button that has content_desc "more options"
+- action 5: jade green touched on a button that has resource_id "android:id/expand_activities_button"
+- action 6: jade green touched on a button that has content_desc "more options"
+- action 7: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "view last captured media"
 - action 2: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "view last captured media"
-- action 2: touched on a button that has content-desc "more options"
-- action 3: touched on a button that has text "set picture as"
-- action 4: touched on a button that has text "gallery, wallpaper"
-- action 6: touched on a button that has content-desc "more options"
-- action 7: press the back button 2 times because you stayed on the pages not belonging to the target app for too long
-- action 8: touched on a button that has content-desc "view last captured media"
-- action 9: touched on a button that has content-desc "more options"
-- action 10: touched on a button that has text "set picture as"
-- action 11: touched on a button that has text "gallery, wallpaper"
-- action 13: touched on a button that has content-desc "more options"
-- action 14: press the back button 2 times because you stayed on the pages not belonging to the target app for too long
-- action 15: touched on a button that has content-desc "view last captured media"
-- action 16: task completed?</t>
+    <t>- action 2: jade green touched on a button that has content_desc "view last captured media"
+- action 3: jade green touched on a button that has text "just once"
+- action 4: jade green touched on a button that has content_desc "share with print"
+- action 5: task completed?</t>
   </si>
   <si>
     <t>- action 3: touched on a button that has text "video"
@@ -1246,36 +1199,32 @@
 - action 6: task completed?</t>
   </si>
   <si>
-    <t>- action 3: touched on a button that has text "camera"
-- action 4: touched on a button that has content-desc "shutter"
-- action 5: touched on a button that has content-desc "shutter"
-- action 6: touched on a button that has content-desc "view last captured media"
-- action 7: touched on a button that has content-desc "more options"
-- action 8: touched on a button that has text "details"
-- action 9: touched on a button that has text "close"
-- action 11: touched on a button that has content-desc "view last captured media"
-- action 12: touched on a button that has content-desc "more options"
-- action 13: touched on a button that has text "details"
-- action 14: touched on a button that has text "close"
-- action 15: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has text "photo"
-- action 2: touched on a button that has content-desc "shutter"
-- action 3: touched on a button that has content-desc "settings"
-- action 5: touched on a button that has text "photo compression quality, 50%"
-- action 7: touched on a button that has text "photo compression quality, 50%"
-- action 9: touched on a button that has text "photo compression quality, 50%"
-- action 11: touched on a button that has text "photo compression quality, 50%"
-- action 13: touched on a button that has text "photo compression quality, 50%"
-- action 14: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "view last captured media"
-- action 2: touched on a button that has content-desc "more options"
-- action 3: touched on a button that has text "rotate right"
-- action 4: touched on a button that has content-desc "more options"
-- action 5: touched on a button that has content-desc "more options"
+    <t>- action 1: jade green waited for a loading state to finish
+- action 2: jade green touched on a button that has content_desc "view last captured media"
+- action 3: jade green touched on a button that has text "just once"
+- action 4: jade green touched on a button that has content_desc "more options"
+- action 6: jade green touched on a button that has content_desc "view last captured media"
+- action 7: jade green touched on a button that has text "just once"
+- action 8: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "view last captured media"
+- action 2: jade green touched on a button that has text "just once"
+- action 3: jade green touched on a button that has content_desc "more options"
+- action 4: jade green touched on a button that has content_desc "dcim, navigate up"
+- action 5: jade green touched on a button that has content_desc "share with print"
+- action 6: jade green long touched on a button that has content_desc "share with print"
+- action 8: jade green touched on a button that has content_desc "view last captured media"
+- action 9: jade green touched on a button that has text "just once"
+- action 10: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "view last captured media"
+- action 2: jade green touched on a button that has text "just once"
+- action 3: jade green touched on a button that has content_desc "more options"
+- action 4: jade green touched on a button that has content_desc "dcim, navigate up"
+- action 5: jade green touched on a button that has content_desc "more options"
+- action 6: press the back button because you stayed on the pages not belonging to the target app for too long
 - action 7: task completed?</t>
   </si>
   <si>
@@ -1314,12 +1263,8 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "settings"
-- action 3: touched on a button that has text "max reminder duration, 5 minutes"
-- action 6: touched on a button that has text "snooze time, 5 minutes"
-- action 9: touched on a button that has text "always use same snooze time"
-- action 12: touched on a button that has text "max reminder duration, 5 minutes"
-- action 14: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "sort by"
+- action 2: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "timer"
@@ -1406,12 +1351,18 @@
 - action 6: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 3: touched on a button that has content-desc "more options"
-- action 5: touched on a button that has content-desc "more options"
-- action 7: touched on a button that has content-desc "more options"
-- action 9: touched on a button that has content-desc "more options"
-- action 10: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "back"
+- action 2: jade green touched on a button that has content_desc "create group"
+- action 3: jade green filled a focused textfield that has text "title" with the text "classmates"
+- action 4: jade green touched on a button that has text "ok"
+- action 5: jade green touched on a button that has text "classmates (4)"
+- action 6: jade green touched on a button that has content_desc "send sms to group"
+- action 7: jade green long touched on a button that has text "john smith"
+- action 8: jade green touched on a button that has content_desc "done"
+- action 9: jade green long touched on a button that has text "31232134"
+- action 10: jade green touched on a button that has content_desc "edit contact"
+- action 11: jade green touched on a button that has content_desc "delete"
+- action 12: task completed?</t>
   </si>
   <si>
     <t>- action 1: long touched on a button that has text "bob"
@@ -1421,18 +1372,9 @@
 - action 5: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "settings"
-- action 3: touched on a button that has text "manage shown tabs"
-- action 5: touched on a button that has text "manage shown tabs"
-- action 6: touched on a checked checkbox that has text "groups"
-- action 7: touched on a checked checkbox that has text "favorites"
-- action 8: touched on a button that has text "ok"
-- action 9: touched on a button that has text "manage shown tabs"
-- action 10: touched on a checkbox that has text "favorites"
-- action 11: touched on a button that has text "ok"
-- action 13: touched on a checkbox that has text "show a dialpad button on the main screen"
-- action 14: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "settings"
+- action 3: jade green touched on a checked checkbox that has text "show a dialpad button on the main screen"
+- action 4: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "more options"
@@ -1448,19 +1390,14 @@
 - action 3: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "dialpad"
-- action 4: touched on a button that has content-desc "more options"
-- action 5: touched on a button that has text "dialpad"
-- action 7: touched on a button that has content-desc "more options"
-- action 8: touched on a button that has text "dialpad"
-- action 10: touched on a button that has content-desc "create new contact"
-- action 12: touched on a button that has content-desc "more options"
-- action 13: touched on a button that has text "dialpad"
-- action 15: touched on a button that has content-desc "more options"
-- action 16: touched on a button that has text "dialpad"
-- action 18: touched on a button that has content-desc "sort by"
-- action 19: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "call number"
+- action 2: jade green touched on a button that has content_desc "dialpad"
+- action 3: jade green filled a focused textfield that has resource_id "com.simplemobiletools.dialer:id/dialpad_input" with the text "911"
+- action 4: jade green touched on a button that has content_desc "call number"
+- action 5: jade green touched on a button that has content_desc "dialpad"
+- action 6: jade green touched on a button that has content_desc "call number"
+- action 7: jade green filled a focused textfield that has resource_id "com.simplemobiletools.dialer:id/dialpad_input" with the text "911"
+- action 8: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "bob"
@@ -1477,9 +1414,9 @@
 - action 5: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "settings"
-- action 3: touched on a button that has text "manage shown contact fields"
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "settings"
+- action 3: jade green touched on a button that has text "manage shown contact fields"
 - action 4: task completed?</t>
   </si>
   <si>
@@ -1508,20 +1445,11 @@
 - action 5: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "dialpad"
-- action 2: filled a focused textfield that has resource_id "com.simplemobiletools.dialer:id/dialpad_input" with the text "911"
-- action 3: touched on a button that has content-desc "call number"
-- action 5: touched on a button that has content-desc "call number"
-- action 7: touched on a button that has content-desc "call number"
-- action 9: touched on a button that has content-desc "call number"
-- action 11: touched on a button that has content-desc "call number"
-- action 13: touched on a button that has content-desc "call number"
-- action 15: touched on a button that has content-desc "call number"
-- action 17: touched on a button that has content-desc "call number"
-- action 19: touched on a button that has content-desc "call number"
-- action 21: touched on a button that has content-desc "call number"
-- action 23: touched on a button that has content-desc "call number"
-- action 25: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "back"
+- action 2: jade green touched on a button that has content_desc "dialpad"
+- action 3: jade green filled a focused textfield that has resource_id "com.simplemobiletools.dialer:id/dialpad_input" with the text "911"
+- action 4: jade green touched on a button that has content_desc "call number"
+- action 5: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "alice"
@@ -1541,26 +1469,21 @@
 - action 7: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "back"
-- action 3: touched on a button that has text "phone"
-- action 4: touched on a button that has text "call history"
-- action 5: touched on a button that has text "call history"
-- action 6: touched on a button that has text "call history"
-- action 7: touched on a button that has text "call history"
-- action 8: touched on a button that has text "call history"
-- action 9: touched on a button that has text "call history"
-- action 10: touched on a button that has text "call history"
-- action 11: touched on a button that has text "call history"
-- action 12: touched on a button that has text "call history"
-- action 13: touched on a button that has text "call history"
-- action 14: touched on a button that has text "call history"
-- action 15: task completed?</t>
+    <t>- action 1: jade green touched on a button that has text "call history"
+- action 2: jade green touched on a button that has content_desc "clear call history"
+- action 3: jade green touched on a button that has text "yes"
+- action 4: task completed?</t>
   </si>
   <si>
     <t>- action 1: long touched on a button that has text "jack"
 - action 2: touched on a button that has content-desc "delete"
 - action 3: touched on a button that has text "yes"
 - action 4: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has text "call history"
+- action 2: jade green touched on a button that has content_desc "search"
+- action 3: task completed?</t>
   </si>
   <si>
     <t>- action 2: touched on a button that has text "alice"
@@ -1604,8 +1527,9 @@
 - action 3: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "settings"
-- action 14: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "settings"
+- action 5: jade green touched on a button that has text "sd card, 835.5 mb, free[...and more]"
+- action 6: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "settings"
@@ -1642,11 +1566,11 @@
 - action 3: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "apps list"
-- action 2: touched on a button that has text "recents"
-- action 6: touched on a button that has content-desc "search"
-- action 7: filled a focused textfield that has text "search" with the text "test1.m4a"
-- action 8: task completed?</t>
+    <t>- action 2: jade green touched on a button that has text "files"
+- action 5: jade green touched on a button that has text "files"
+- action 8: jade green touched on a button that has content_desc "search"
+- action 9: jade green filled a focused textfield that has text "search" with the text "test1.m4a"
+- action 10: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "android, 3 items"
@@ -1679,9 +1603,10 @@
 - action 5: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "settings"
-- action 2: touched on a checkbox that has text "show hidden items"
-- action 3: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "settings"
+- action 2: jade green touched on a checked checkbox that has text "show hidden items"
+- action 3: jade green touched on a checkbox that has text "show hidden items"
+- action 4: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "more options"
@@ -1697,11 +1622,11 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "settings"
-- action 9: touched on a checked checkbox that has text "gifs"
-- action 10: touched on a button that has text "ok"
-- action 11: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "settings"
+- action 10: jade green touched on a button that has text "file thumbnail style"
+- action 11: jade green touched on a checkbox that has text "animate gifs at thumbnails"
+- action 12: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "dcim, 3, /storage/emulated/0/"
@@ -1766,24 +1691,27 @@
 - action 4: task completed?</t>
   </si>
   <si>
+    <t>- action 1: jade green touched on a button that has content_desc "settings"
+- action 5: task completed?</t>
+  </si>
+  <si>
     <t>- action 1: touched on a button that has text "alice, i love you, 09.09"
 - action 2: filled a textfield that has text "type a messageâ€¦" with the text "morning"
 - action 3: touched on a button that has text "sms"
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has resource_id "com.simplemobiletools.smsmessenger:id/conversations_fab"
-- action 2: filled a focused textfield that has text "add contact or numberâ€¦" with the text "1234567890"
-- action 3: touched on a button that has resource_id "com.simplemobiletools.smsmessenger:id/new_conversation_confirm"
-- action 4: filled a textfield that has text "type a messageâ€¦" with the text "hi there! this is a test message to check how the mms functionality works in the sms messenger app. i hope this long message is sent successfully as an mms. have a great day!"
-- action 5: touched on a button that has text "sms"
-- action 6: touched on a button that has content-desc "attachment"
-- action 7: touched on a button that has text "choose photo"
-- action 9: touched on a button that has text "choose photo"
-- action 11: touched on a button that has text "choose photo"
-- action 12: touched on a button that has text "large files"
-- action 13: touched on a button that has content-desc "list view"
-- action 14: task completed?</t>
+    <t>- action 1: jade green touched on a button that has text "start a conversation"
+- action 2: jade green touched on a button that has text "alice, 1234567890"
+- action 3: jade green touched on a button that has content_desc "attachment"
+- action 4: jade green touched on a button that has text "choose photo"
+- action 5: jade green touched on a button that has content_desc "show roots"
+- action 6: jade green touched on a button that has text "images"
+- action 8: jade green filled a textfield that has text "hi alice, i wanted to share some exciting news wit[...]" with the text "hi alice, i wanted to share some exciting news with you! i've been working on a new project that combines my passion for technology and sustainability. it's been an incredible journey so far, and i can't wait to tell you all about it. let's catch up soon over coffee or a call!"
+- action 9: jade green touched on a button that has text "sms"
+- action 10: jade green touched on a button that has content_desc "attachment"
+- action 11: jade green touched on a button that has text "choose photo"
+- action 12: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "settings"
@@ -1809,17 +1737,13 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: long touched on a button that has text "alice, i love you, 09.09"
-- action 2: touched on a button that has content-desc "more options"
-- action 4: long touched on a selected button that has text "alice, i love you, 09.09"
-- action 5: touched on a button that has content-desc "more options"
-- action 7: touched on a button that has content-desc "more options"
-- action 8: touched on a button that has text "archive"
-- action 9: touched on a button that has text "no"
-- action 10: long touched on a button that has content-desc "more options"
-- action 11: touched on a button that has content-desc "more options"
-- action 13: touched on a button that has content-desc "more options"
-- action 14: task completed?</t>
+    <t>- action 2: jade green touched on a button that has text "alice, hi alice, i wanted to share some exciting news wit[...], 05:14 pm"
+- action 3: jade green touched on a button that has content_desc "more options"
+- action 4: jade green touched on a button that has text "conversation details"
+- action 5: jade green touched on a button that has text "alice"
+- action 6: jade green filled a focused textfield that has text "conversation name" with the text "team_discussion"
+- action 7: jade green touched on a button that has text "ok"
+- action 8: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "alice, draft, hi alice, this is a test message to see how the mm[...][...and more]"
@@ -1840,33 +1764,19 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "settings"
-- action 3: touched on a button that has text "manage shown tabs"
-- action 5: touched on a button that has text "gapless playback"
-- action 6: touched on a button that has text "customize colors"
-- action 8: touched on a button that has text "manage excluded folders"
-- action 9: touched on a button that has content-desc "back"
-- action 10: touched on a button that has text "manage shown tabs"
-- action 11: touched on a checkbox that has text "genres"
-- action 13: touched on a button that has content-desc "back"
-- action 14: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "equalizer"
+- action 2: jade green touched on a button that has text "hip hop"
+- action 3: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "recordings, 3 tracks"
 - action 2: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has text "test1, &lt;unknown&gt; â€¢ recordings, 00:03"
-- action 2: touched on a button that has content-desc "play / pause"
-- action 3: touched on a button that has content-desc "more options"
-- action 5: touched on a button that has content-desc "more options"
-- action 7: touched on a button that has content-desc "more options"
-- action 9: touched on a button that has content-desc "more options"
-- action 11: touched on a button that has content-desc "back"
-- action 12: touched on a button that has content-desc "repeat all"
-- action 13: touched on a button that has content-desc "repeat current song"
-- action 14: task completed?</t>
+    <t>- action 1: jade green touched on a button that has text "folders"
+- action 2: jade green touched on a button that has text "recordings, 8 tracks"
+- action 3: jade green touched on a button that has text "test1, &lt;unknown&gt; • recordings, 00:01"
+- action 4: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "tracks"
@@ -1916,14 +1826,12 @@
 - action 6: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "create a new note"
-- action 2: filled a focused textfield that has text "label" with the text "test"
-- action 3: touched on a button that has text "ok"
-- action 4: filled a focused textfield that has text "test" with the text "12345678"
-- action 6: touched on a focused textfield that has text "12345678"
-- action 9: touched on a button that has content-desc "search"
-- action 10: filled a focused textfield that has text "search" with the text "234"
-- action 11: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "create a new note"
+- action 2: jade green filled a focused textfield that has text "label" with the text "test"
+- action 3: jade green touched on a button that has text "ok"
+- action 4: jade green filled a focused textfield that has text "insert text here" with the text "12345678"
+- action 5: jade green touched on a button that has content_desc "search"
+- action 6: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "create a new note"
@@ -1932,14 +1840,14 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: long touched on a button that has content-desc "more options"
-- action 2: long touched on a button that has content-desc "more options"
-- action 3: touched on a button that has content-desc "open note"
-- action 4: long touched on a button that has text "diary"
-- action 5: touched on a button that has content-desc "more options"
-- action 6: touched on a button that has text "delete note"
-- action 7: touched on a button that has text "delete"
-- action 8: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "search"
+- action 2: jade green filled a focused textfield that has text "search" with the text "diary"
+- action 3: jade green touched on a button that has content_desc "next"
+- action 4: jade green touched on a button that has content_desc "open note"
+- action 6: jade green touched on a button that has content_desc "more options"
+- action 7: jade green touched on a button that has text "delete note"
+- action 8: jade green touched on a button that has text "delete"
+- action 9: task completed?</t>
   </si>
   <si>
     <t>- action 1: long touched on a button that has content-desc "more options"
@@ -1971,16 +1879,14 @@
 - action 5: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "open note"
-- action 2: touched on a button that has text "diary"
-- action 3: touched on a button that has text "general note"
-- action 4: touched on a button that has text "diary"
-- action 5: touched on a button that has content-desc "more options"
-- action 6: touched on a button that has text "export as file"
-- action 7: filled a textfield that has text "diary.txt" with the text "diary.txt"
-- action 8: touched on a button that has text "save"
-- action 9: touched on a button that has text "only export the current file content
-- action 11: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "search"
+- action 2: jade green filled a focused textfield that has text "search" with the text "diary"
+- action 3: jade green touched on a button that has content_desc "more options"
+- action 4: jade green touched on a button that has text "export as file"
+- action 5: jade green filled a textfield that has text "general note.txt" with the text "diary.txt"
+- action 6: jade green touched on a button that has text "save"
+- action 7: jade green touched on a button that has text "only export the current file content
+- action 8: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "general note"
@@ -2023,12 +1929,8 @@
 - action 3: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "search"
-- action 2: filled a focused textfield that has text "search" with the text "test1"
-- action 3: touched on a button that has text "test1.m4a, 00:05, 12.08.2024, 06:00 pm[...and more]"
-- action 4: touched on a button that has text "test1.m4a, 00:05, 12.08.2024, 06:00 pm[...and more]"
-- action 5: touched on a button that has content-desc "play / pause"
-- action 6: task completed?</t>
+    <t>- action 1: jade green filled a textfield that has text "search" with the text "test1"
+- action 2: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "settings"
@@ -2080,21 +1982,20 @@
   </si>
   <si>
     <t>False
-False
-False
 True
-True
-False</t>
-  </si>
-  <si>
-    <t>False
-False
-False
 False
 False
 True
 True
 True
+True
+True</t>
+  </si>
+  <si>
+    <t>True
+True
+True
+True
 True</t>
   </si>
   <si>
@@ -2104,8 +2005,6 @@
   </si>
   <si>
     <t>False
-False
-False
 False
 False
 False
@@ -2136,18 +2035,8 @@
 True
 True
 True
+True
 True</t>
-  </si>
-  <si>
-    <t>False
-False
-False
-False
-False
-False
-False
-False
-False</t>
   </si>
   <si>
     <t>True
@@ -2165,31 +2054,38 @@
   <si>
     <t>True
 False
-True
-True
-True
+False
+False
+False
+False
+False
+False
+False</t>
+  </si>
+  <si>
+    <t>True
 False
 True
 False
 False
+False
+False</t>
+  </si>
+  <si>
+    <t>True
 True</t>
   </si>
   <si>
     <t>True
 True
 True
-True
-True
+False
+False
+False
 False</t>
   </si>
   <si>
     <t>True
-True</t>
-  </si>
-  <si>
-    <t>True
-True
-False
 False
 True
 False
@@ -2197,20 +2093,12 @@
 False
 False
 False
-True
+False</t>
+  </si>
+  <si>
+    <t>True
 False
 False
-False</t>
-  </si>
-  <si>
-    <t>False
-False
-True
-True
-True
-False
-False
-True
 False
 False
 False
@@ -2218,11 +2106,7 @@
   </si>
   <si>
     <t>True
-True
-True
-False
-False
-True</t>
+False</t>
   </si>
   <si>
     <t>True
@@ -2230,10 +2114,8 @@
 True
 True
 True
-True</t>
-  </si>
-  <si>
-    <t>False
+True
+False
 False
 False
 False
@@ -2248,22 +2130,20 @@
 False
 False
 False
+False</t>
+  </si>
+  <si>
+    <t>True
+True
+False</t>
+  </si>
+  <si>
+    <t>False
 False
-False
-False
-True
-True</t>
+False</t>
   </si>
   <si>
     <t>False
-True
-False
-False
-False
-False
-False
-False
-False
 False
 False
 False
@@ -2271,143 +2151,26 @@
   </si>
   <si>
     <t>True
-True
-False
-False</t>
-  </si>
-  <si>
-    <t>True
-True
-True
-False
-False
-False
-False
-False
-False
-False
-False
-False
-False
-True</t>
-  </si>
-  <si>
-    <t>False
-True
-False
-False
-False
-False
-False
-False
-False
-False
 False
 False
 False
 False</t>
   </si>
   <si>
-    <t>False
+    <t>True
+True
+True
 False</t>
-  </si>
-  <si>
-    <t>False
-True
-False
-True
-True</t>
   </si>
   <si>
     <t>False
 False
-False</t>
-  </si>
-  <si>
-    <t>True
-False</t>
-  </si>
-  <si>
-    <t>False
-False
-False
-False
-False
-False
-False
-False
-False
-False
-False
-False</t>
-  </si>
-  <si>
-    <t>True
-True
-False
-True
-True
 False
 False
 True
 True
 True
 False</t>
-  </si>
-  <si>
-    <t>False
-False
-False
-False
-False
-False
-False
-False
-False
-False
-False</t>
-  </si>
-  <si>
-    <t>True
-True
-False
-False
-False
-False
-False
-True
-True
-True</t>
-  </si>
-  <si>
-    <t>False
-False
-True
-True
-True
-True
-True
-True</t>
-  </si>
-  <si>
-    <t>False
-False
-True
-True
-True
-True
-True
-True
-True
-True</t>
-  </si>
-  <si>
-    <t>True
-True
-True
-False
-True
-True</t>
   </si>
   <si>
     <t xml:space="preserve">- ACTION 1: touched on a button that has content-desc "More options"
@@ -3320,87 +3083,12 @@
 - ACTION 2: touched on a button that has text "test2.m4a"
 </t>
   </si>
-  <si>
-    <t>note</t>
-  </si>
-  <si>
-    <t>if can execute more steps -&gt; can be success</t>
-  </si>
-  <si>
-    <t>loop</t>
-  </si>
-  <si>
-    <t>not save</t>
-  </si>
-  <si>
-    <t>PERFECT</t>
-  </si>
-  <si>
-    <t>valid because of precondition, it have not enabled yet so it enable before disable the option</t>
-  </si>
-  <si>
-    <t>WRONG CONTEXT (soa is 111111111 while task_desc is 2222222)</t>
-  </si>
-  <si>
-    <t>Forget to click "OK"</t>
-  </si>
-  <si>
-    <t>maybe scroll is good but with my data, it does not have to scroll</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scroll down maybe an </t>
-  </si>
-  <si>
-    <t>cannot stop app/ however it called 911 successfully</t>
-  </si>
-  <si>
-    <t>wrong precondition</t>
-  </si>
-  <si>
-    <t>loop spamming "CAll History"</t>
-  </si>
-  <si>
-    <t>invalid preconditon</t>
-  </si>
-  <si>
-    <t>different day time created -&gt; cannot select</t>
-  </si>
-  <si>
-    <t>precondition failed</t>
-  </si>
-  <si>
-    <t>untick before end task</t>
-  </si>
-  <si>
-    <t>invalid precondition</t>
-  </si>
-  <si>
-    <t>close before press call</t>
-  </si>
-  <si>
-    <t>Maybe need to click download PDF or is it just ok (if click print is success goal =&gt; this task is valid and optimal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">invalid precondition =&gt; if on existed diary =&gt; this is optimal and valid </t>
-  </si>
-  <si>
-    <t>test_script_eval</t>
-  </si>
-  <si>
-    <t>data change</t>
-  </si>
-  <si>
-    <t>permission granted, does not need to do again</t>
-  </si>
-  <si>
-    <t>navigating to a wrong date as date changed</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3463,21 +3151,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3515,7 +3195,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -3549,7 +3229,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -3584,10 +3263,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3760,15 +3438,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P151"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="54.08984375" customWidth="1"/>
-    <col min="7" max="7" width="8.90625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N151"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3811,14 +3485,8 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -3832,7 +3500,7 @@
         <v>318</v>
       </c>
       <c r="E2" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -3841,7 +3509,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -3861,11 +3529,8 @@
       <c r="N2">
         <v>1</v>
       </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -3879,7 +3544,7 @@
         <v>319</v>
       </c>
       <c r="E3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -3888,7 +3553,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -3908,11 +3573,8 @@
       <c r="N3">
         <v>1</v>
       </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -3926,7 +3588,7 @@
         <v>320</v>
       </c>
       <c r="E4" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -3935,7 +3597,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
@@ -3955,11 +3617,8 @@
       <c r="N4">
         <v>1</v>
       </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -3973,7 +3632,7 @@
         <v>321</v>
       </c>
       <c r="E5" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -3982,7 +3641,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -4002,11 +3661,8 @@
       <c r="N5">
         <v>1</v>
       </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -4020,7 +3676,7 @@
         <v>322</v>
       </c>
       <c r="E6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -4029,7 +3685,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -4049,11 +3705,8 @@
       <c r="N6">
         <v>1</v>
       </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -4067,7 +3720,7 @@
         <v>323</v>
       </c>
       <c r="E7" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -4076,7 +3729,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -4096,11 +3749,8 @@
       <c r="N7">
         <v>1</v>
       </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -4114,43 +3764,37 @@
         <v>324</v>
       </c>
       <c r="E8" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="I8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>0.33333333333333331</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N8">
         <v>0</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -4164,16 +3808,16 @@
         <v>325</v>
       </c>
       <c r="E9" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
       <c r="G9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -4182,22 +3826,19 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>0.44444444444444442</v>
+        <v>1</v>
       </c>
       <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>15</v>
       </c>
@@ -4211,7 +3852,7 @@
         <v>326</v>
       </c>
       <c r="E10" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -4220,7 +3861,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -4240,11 +3881,8 @@
       <c r="N10">
         <v>1</v>
       </c>
-      <c r="O10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -4258,43 +3896,37 @@
         <v>327</v>
       </c>
       <c r="E11" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="I11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="b">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L11">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -4308,7 +3940,7 @@
         <v>328</v>
       </c>
       <c r="E12" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
@@ -4317,7 +3949,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -4329,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M12">
         <v>0</v>
@@ -4337,11 +3969,8 @@
       <c r="N12">
         <v>0</v>
       </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -4355,7 +3984,7 @@
         <v>329</v>
       </c>
       <c r="E13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -4364,7 +3993,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
@@ -4384,14 +4013,8 @@
       <c r="N13">
         <v>1</v>
       </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -4405,7 +4028,7 @@
         <v>330</v>
       </c>
       <c r="E14" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -4414,7 +4037,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -4434,11 +4057,8 @@
       <c r="N14">
         <v>1</v>
       </c>
-      <c r="O14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -4452,7 +4072,7 @@
         <v>331</v>
       </c>
       <c r="E15" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -4461,7 +4081,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -4481,11 +4101,8 @@
       <c r="N15">
         <v>1</v>
       </c>
-      <c r="O15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -4499,7 +4116,7 @@
         <v>332</v>
       </c>
       <c r="E16" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -4508,7 +4125,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
@@ -4528,11 +4145,8 @@
       <c r="N16">
         <v>1</v>
       </c>
-      <c r="O16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -4546,7 +4160,7 @@
         <v>333</v>
       </c>
       <c r="E17" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -4555,7 +4169,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -4575,11 +4189,8 @@
       <c r="N17">
         <v>1</v>
       </c>
-      <c r="O17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -4593,7 +4204,7 @@
         <v>334</v>
       </c>
       <c r="E18" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -4602,7 +4213,7 @@
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
@@ -4622,11 +4233,8 @@
       <c r="N18">
         <v>1</v>
       </c>
-      <c r="O18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -4640,40 +4248,37 @@
         <v>335</v>
       </c>
       <c r="E19" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="I19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -4687,7 +4292,7 @@
         <v>336</v>
       </c>
       <c r="E20" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -4696,7 +4301,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="I20" t="b">
         <v>1</v>
@@ -4716,11 +4321,8 @@
       <c r="N20">
         <v>1</v>
       </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -4734,7 +4336,7 @@
         <v>337</v>
       </c>
       <c r="E21" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -4743,7 +4345,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="I21" t="b">
         <v>1</v>
@@ -4763,11 +4365,8 @@
       <c r="N21">
         <v>1</v>
       </c>
-      <c r="O21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -4781,16 +4380,16 @@
         <v>338</v>
       </c>
       <c r="E22" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="b">
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -4799,22 +4398,19 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>0.6</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="N22">
-        <v>0.1</v>
-      </c>
-      <c r="O22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -4828,7 +4424,7 @@
         <v>339</v>
       </c>
       <c r="E23" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -4837,7 +4433,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="I23" t="b">
         <v>1</v>
@@ -4857,11 +4453,8 @@
       <c r="N23">
         <v>1</v>
       </c>
-      <c r="O23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
         <v>16</v>
       </c>
@@ -4875,7 +4468,7 @@
         <v>340</v>
       </c>
       <c r="E24" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -4884,7 +4477,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="I24" t="b">
         <v>1</v>
@@ -4904,11 +4497,8 @@
       <c r="N24">
         <v>1</v>
       </c>
-      <c r="O24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
         <v>16</v>
       </c>
@@ -4922,7 +4512,7 @@
         <v>341</v>
       </c>
       <c r="E25" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -4931,7 +4521,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="I25" t="b">
         <v>1</v>
@@ -4951,11 +4541,8 @@
       <c r="N25">
         <v>1</v>
       </c>
-      <c r="O25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -4969,7 +4556,7 @@
         <v>342</v>
       </c>
       <c r="E26" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -4978,7 +4565,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="I26" t="b">
         <v>1</v>
@@ -4998,11 +4585,8 @@
       <c r="N26">
         <v>1</v>
       </c>
-      <c r="O26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
         <v>16</v>
       </c>
@@ -5016,7 +4600,7 @@
         <v>343</v>
       </c>
       <c r="E27" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -5025,7 +4609,7 @@
         <v>1</v>
       </c>
       <c r="H27" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="I27" t="b">
         <v>1</v>
@@ -5045,11 +4629,8 @@
       <c r="N27">
         <v>1</v>
       </c>
-      <c r="O27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
         <v>16</v>
       </c>
@@ -5063,7 +4644,7 @@
         <v>344</v>
       </c>
       <c r="E28" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -5072,31 +4653,28 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>0.83333333333333337</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="N28">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.1428571428571428</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -5110,7 +4688,7 @@
         <v>345</v>
       </c>
       <c r="E29" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -5119,7 +4697,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="I29" t="b">
         <v>1</v>
@@ -5139,11 +4717,8 @@
       <c r="N29">
         <v>1</v>
       </c>
-      <c r="O29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
         <v>16</v>
       </c>
@@ -5157,19 +4732,19 @@
         <v>346</v>
       </c>
       <c r="E30" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="I30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
@@ -5178,22 +4753,16 @@
         <v>4</v>
       </c>
       <c r="L30">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M30">
-        <v>0.2857142857142857</v>
+        <v>1</v>
       </c>
       <c r="N30">
-        <v>0.14285714285714279</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -5207,7 +4776,7 @@
         <v>347</v>
       </c>
       <c r="E31" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -5216,7 +4785,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="I31" t="b">
         <v>1</v>
@@ -5236,11 +4805,8 @@
       <c r="N31">
         <v>1</v>
       </c>
-      <c r="O31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -5263,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -5272,22 +4838,19 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L32">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M32">
-        <v>0.33333333333333331</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.4285714285714285</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" t="s">
         <v>16</v>
       </c>
@@ -5301,7 +4864,7 @@
         <v>349</v>
       </c>
       <c r="E33" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
@@ -5310,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -5319,22 +4882,19 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33">
         <v>9</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34" t="s">
         <v>16</v>
       </c>
@@ -5348,16 +4908,16 @@
         <v>350</v>
       </c>
       <c r="E34" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="b">
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -5366,22 +4926,19 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M34">
-        <v>0.66666666666666663</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N34">
-        <v>0.5</v>
-      </c>
-      <c r="O34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.1428571428571428</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -5395,7 +4952,7 @@
         <v>351</v>
       </c>
       <c r="E35" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -5404,7 +4961,7 @@
         <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="I35" t="b">
         <v>1</v>
@@ -5424,14 +4981,8 @@
       <c r="N35">
         <v>1</v>
       </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36" t="s">
         <v>16</v>
       </c>
@@ -5445,7 +4996,7 @@
         <v>352</v>
       </c>
       <c r="E36" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -5454,7 +5005,7 @@
         <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="I36" t="b">
         <v>1</v>
@@ -5474,11 +5025,8 @@
       <c r="N36">
         <v>1</v>
       </c>
-      <c r="O36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -5492,7 +5040,7 @@
         <v>353</v>
       </c>
       <c r="E37" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -5501,7 +5049,7 @@
         <v>1</v>
       </c>
       <c r="H37" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="I37" t="b">
         <v>1</v>
@@ -5521,14 +5069,8 @@
       <c r="N37">
         <v>1</v>
       </c>
-      <c r="O37">
-        <v>1</v>
-      </c>
-      <c r="P37" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38" t="s">
         <v>16</v>
       </c>
@@ -5542,7 +5084,7 @@
         <v>354</v>
       </c>
       <c r="E38" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -5551,7 +5093,7 @@
         <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -5571,11 +5113,8 @@
       <c r="N38">
         <v>1</v>
       </c>
-      <c r="O38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -5589,7 +5128,7 @@
         <v>355</v>
       </c>
       <c r="E39" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -5598,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="I39" t="b">
         <v>1</v>
@@ -5618,11 +5157,8 @@
       <c r="N39">
         <v>1</v>
       </c>
-      <c r="O39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -5636,7 +5172,7 @@
         <v>356</v>
       </c>
       <c r="E40" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -5645,7 +5181,7 @@
         <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="I40" t="b">
         <v>1</v>
@@ -5665,11 +5201,8 @@
       <c r="N40">
         <v>1</v>
       </c>
-      <c r="O40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
         <v>17</v>
       </c>
@@ -5692,31 +5225,28 @@
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="I41" t="b">
         <v>0</v>
       </c>
       <c r="J41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N41">
-        <v>0</v>
-      </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
         <v>17</v>
       </c>
@@ -5730,7 +5260,7 @@
         <v>358</v>
       </c>
       <c r="E42" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
@@ -5739,7 +5269,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="I42" t="b">
         <v>1</v>
@@ -5759,11 +5289,8 @@
       <c r="N42">
         <v>1</v>
       </c>
-      <c r="O42">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
         <v>17</v>
       </c>
@@ -5777,7 +5304,7 @@
         <v>359</v>
       </c>
       <c r="E43" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -5786,7 +5313,7 @@
         <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="I43" t="b">
         <v>1</v>
@@ -5806,11 +5333,8 @@
       <c r="N43">
         <v>1</v>
       </c>
-      <c r="O43">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -5824,7 +5348,7 @@
         <v>360</v>
       </c>
       <c r="E44" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -5833,7 +5357,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="I44" t="b">
         <v>1</v>
@@ -5853,11 +5377,8 @@
       <c r="N44">
         <v>1</v>
       </c>
-      <c r="O44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45" t="s">
         <v>17</v>
       </c>
@@ -5871,7 +5392,7 @@
         <v>361</v>
       </c>
       <c r="E45" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F45" t="b">
         <v>1</v>
@@ -5880,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="I45" t="b">
         <v>1</v>
@@ -5900,11 +5421,8 @@
       <c r="N45">
         <v>1</v>
       </c>
-      <c r="O45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -5918,7 +5436,7 @@
         <v>362</v>
       </c>
       <c r="E46" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
@@ -5927,7 +5445,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="I46" t="b">
         <v>1</v>
@@ -5947,14 +5465,8 @@
       <c r="N46">
         <v>1</v>
       </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
-      <c r="P46" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
         <v>17</v>
       </c>
@@ -5968,7 +5480,7 @@
         <v>363</v>
       </c>
       <c r="E47" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
@@ -5977,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="I47" t="b">
         <v>1</v>
@@ -5997,11 +5509,8 @@
       <c r="N47">
         <v>1</v>
       </c>
-      <c r="O47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -6015,7 +5524,7 @@
         <v>364</v>
       </c>
       <c r="E48" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
@@ -6024,7 +5533,7 @@
         <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="I48" t="b">
         <v>1</v>
@@ -6044,11 +5553,8 @@
       <c r="N48">
         <v>1</v>
       </c>
-      <c r="O48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49" t="s">
         <v>17</v>
       </c>
@@ -6062,7 +5568,7 @@
         <v>365</v>
       </c>
       <c r="E49" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
@@ -6071,7 +5577,7 @@
         <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="I49" t="b">
         <v>1</v>
@@ -6091,11 +5597,8 @@
       <c r="N49">
         <v>1</v>
       </c>
-      <c r="O49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50" t="s">
         <v>17</v>
       </c>
@@ -6109,7 +5612,7 @@
         <v>366</v>
       </c>
       <c r="E50" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
@@ -6118,7 +5621,7 @@
         <v>1</v>
       </c>
       <c r="H50" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="I50" t="b">
         <v>1</v>
@@ -6138,11 +5641,8 @@
       <c r="N50">
         <v>1</v>
       </c>
-      <c r="O50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -6156,7 +5656,7 @@
         <v>367</v>
       </c>
       <c r="E51" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F51" t="b">
         <v>1</v>
@@ -6165,7 +5665,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I51" t="b">
         <v>1</v>
@@ -6185,11 +5685,8 @@
       <c r="N51">
         <v>1</v>
       </c>
-      <c r="O51">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -6203,7 +5700,7 @@
         <v>368</v>
       </c>
       <c r="E52" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F52" t="b">
         <v>1</v>
@@ -6212,7 +5709,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
@@ -6232,14 +5729,8 @@
       <c r="N52">
         <v>1</v>
       </c>
-      <c r="O52">
-        <v>0</v>
-      </c>
-      <c r="P52" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -6253,7 +5744,7 @@
         <v>369</v>
       </c>
       <c r="E53" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
@@ -6262,7 +5753,7 @@
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="I53" t="b">
         <v>1</v>
@@ -6282,11 +5773,8 @@
       <c r="N53">
         <v>1</v>
       </c>
-      <c r="O53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -6300,7 +5788,7 @@
         <v>370</v>
       </c>
       <c r="E54" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F54" t="b">
         <v>1</v>
@@ -6309,7 +5797,7 @@
         <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="I54" t="b">
         <v>1</v>
@@ -6329,11 +5817,8 @@
       <c r="N54">
         <v>1</v>
       </c>
-      <c r="O54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -6347,7 +5832,7 @@
         <v>371</v>
       </c>
       <c r="E55" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
@@ -6356,7 +5841,7 @@
         <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
@@ -6376,11 +5861,8 @@
       <c r="N55">
         <v>1</v>
       </c>
-      <c r="O55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -6394,7 +5876,7 @@
         <v>372</v>
       </c>
       <c r="E56" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
@@ -6403,7 +5885,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="I56" t="b">
         <v>0</v>
@@ -6412,22 +5894,19 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L56">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M56">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N56">
-        <v>0</v>
-      </c>
-      <c r="O56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -6441,7 +5920,7 @@
         <v>373</v>
       </c>
       <c r="E57" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F57" t="b">
         <v>1</v>
@@ -6450,7 +5929,7 @@
         <v>1</v>
       </c>
       <c r="H57" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="I57" t="b">
         <v>1</v>
@@ -6470,11 +5949,8 @@
       <c r="N57">
         <v>1</v>
       </c>
-      <c r="O57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -6488,16 +5964,16 @@
         <v>374</v>
       </c>
       <c r="E58" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="F58" t="b">
         <v>1</v>
       </c>
       <c r="G58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="I58" t="b">
         <v>1</v>
@@ -6506,22 +5982,19 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L58">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M58">
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="N58">
-        <v>0.16666666666666671</v>
-      </c>
-      <c r="O58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -6535,7 +6008,7 @@
         <v>375</v>
       </c>
       <c r="E59" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
@@ -6544,7 +6017,7 @@
         <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="I59" t="b">
         <v>1</v>
@@ -6564,11 +6037,8 @@
       <c r="N59">
         <v>1</v>
       </c>
-      <c r="O59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -6582,7 +6052,7 @@
         <v>376</v>
       </c>
       <c r="E60" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F60" t="b">
         <v>1</v>
@@ -6591,7 +6061,7 @@
         <v>1</v>
       </c>
       <c r="H60" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="I60" t="b">
         <v>1</v>
@@ -6611,11 +6081,8 @@
       <c r="N60">
         <v>1</v>
       </c>
-      <c r="O60">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -6638,7 +6105,7 @@
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="I61" t="b">
         <v>0</v>
@@ -6647,22 +6114,19 @@
         <v>0</v>
       </c>
       <c r="K61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L61">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M61">
-        <v>7.6923076923076927E-2</v>
+        <v>0.25</v>
       </c>
       <c r="N61">
-        <v>0</v>
-      </c>
-      <c r="O61">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -6676,7 +6140,7 @@
         <v>378</v>
       </c>
       <c r="E62" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
@@ -6685,7 +6149,7 @@
         <v>1</v>
       </c>
       <c r="H62" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="I62" t="b">
         <v>1</v>
@@ -6705,11 +6169,8 @@
       <c r="N62">
         <v>1</v>
       </c>
-      <c r="O62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -6723,7 +6184,7 @@
         <v>379</v>
       </c>
       <c r="E63" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F63" t="b">
         <v>1</v>
@@ -6732,7 +6193,7 @@
         <v>1</v>
       </c>
       <c r="H63" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="I63" t="b">
         <v>1</v>
@@ -6752,11 +6213,8 @@
       <c r="N63">
         <v>1</v>
       </c>
-      <c r="O63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:14">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -6770,43 +6228,37 @@
         <v>380</v>
       </c>
       <c r="E64" t="s">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="F64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="I64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" t="b">
         <v>0</v>
       </c>
       <c r="K64">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L64">
         <v>4</v>
       </c>
       <c r="M64">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N64">
-        <v>0.5</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
       <c r="A65" t="s">
         <v>19</v>
       </c>
@@ -6820,7 +6272,7 @@
         <v>381</v>
       </c>
       <c r="E65" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F65" t="b">
         <v>1</v>
@@ -6829,7 +6281,7 @@
         <v>1</v>
       </c>
       <c r="H65" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="I65" t="b">
         <v>1</v>
@@ -6849,14 +6301,8 @@
       <c r="N65">
         <v>1</v>
       </c>
-      <c r="O65">
-        <v>1</v>
-      </c>
-      <c r="P65" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:14">
       <c r="A66" t="s">
         <v>19</v>
       </c>
@@ -6870,7 +6316,7 @@
         <v>382</v>
       </c>
       <c r="E66" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F66" t="b">
         <v>1</v>
@@ -6879,7 +6325,7 @@
         <v>1</v>
       </c>
       <c r="H66" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="I66" t="b">
         <v>1</v>
@@ -6899,11 +6345,8 @@
       <c r="N66">
         <v>1</v>
       </c>
-      <c r="O66">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="1:14">
       <c r="A67" t="s">
         <v>19</v>
       </c>
@@ -6917,7 +6360,7 @@
         <v>319</v>
       </c>
       <c r="E67" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F67" t="b">
         <v>1</v>
@@ -6926,7 +6369,7 @@
         <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="I67" t="b">
         <v>1</v>
@@ -6946,11 +6389,8 @@
       <c r="N67">
         <v>1</v>
       </c>
-      <c r="O67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="1:14">
       <c r="A68" t="s">
         <v>19</v>
       </c>
@@ -6964,7 +6404,7 @@
         <v>383</v>
       </c>
       <c r="E68" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
@@ -6973,7 +6413,7 @@
         <v>1</v>
       </c>
       <c r="H68" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="I68" t="b">
         <v>1</v>
@@ -6993,14 +6433,8 @@
       <c r="N68">
         <v>1</v>
       </c>
-      <c r="O68">
-        <v>1</v>
-      </c>
-      <c r="P68" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="1:14">
       <c r="A69" t="s">
         <v>19</v>
       </c>
@@ -7014,7 +6448,7 @@
         <v>384</v>
       </c>
       <c r="E69" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
@@ -7023,7 +6457,7 @@
         <v>1</v>
       </c>
       <c r="H69" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="I69" t="b">
         <v>1</v>
@@ -7043,11 +6477,8 @@
       <c r="N69">
         <v>1</v>
       </c>
-      <c r="O69">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70" t="s">
         <v>19</v>
       </c>
@@ -7061,43 +6492,37 @@
         <v>385</v>
       </c>
       <c r="E70" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="F70" t="b">
         <v>1</v>
       </c>
       <c r="G70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="I70" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J70" t="b">
         <v>0</v>
       </c>
       <c r="K70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L70">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="M70">
-        <v>0.2857142857142857</v>
+        <v>1</v>
       </c>
       <c r="N70">
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="O70">
-        <v>1</v>
-      </c>
-      <c r="P70" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
       <c r="A71" t="s">
         <v>19</v>
       </c>
@@ -7111,7 +6536,7 @@
         <v>386</v>
       </c>
       <c r="E71" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F71" t="b">
         <v>1</v>
@@ -7120,7 +6545,7 @@
         <v>1</v>
       </c>
       <c r="H71" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="I71" t="b">
         <v>1</v>
@@ -7140,14 +6565,8 @@
       <c r="N71">
         <v>1</v>
       </c>
-      <c r="O71">
-        <v>1</v>
-      </c>
-      <c r="P71" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="72" spans="1:14">
       <c r="A72" t="s">
         <v>19</v>
       </c>
@@ -7161,7 +6580,7 @@
         <v>387</v>
       </c>
       <c r="E72" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F72" t="b">
         <v>1</v>
@@ -7170,7 +6589,7 @@
         <v>1</v>
       </c>
       <c r="H72" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="I72" t="b">
         <v>1</v>
@@ -7190,11 +6609,8 @@
       <c r="N72">
         <v>1</v>
       </c>
-      <c r="O72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="73" spans="1:14">
       <c r="A73" t="s">
         <v>19</v>
       </c>
@@ -7208,43 +6624,37 @@
         <v>388</v>
       </c>
       <c r="E73" t="s">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="F73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="I73" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="b">
         <v>0</v>
       </c>
       <c r="K73">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L73">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="M73">
-        <v>7.1428571428571425E-2</v>
+        <v>1</v>
       </c>
       <c r="N73">
-        <v>0</v>
-      </c>
-      <c r="O73">
-        <v>0</v>
-      </c>
-      <c r="P73" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
       <c r="A74" t="s">
         <v>19</v>
       </c>
@@ -7258,7 +6668,7 @@
         <v>389</v>
       </c>
       <c r="E74" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
@@ -7267,7 +6677,7 @@
         <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="I74" t="b">
         <v>1</v>
@@ -7287,11 +6697,8 @@
       <c r="N74">
         <v>1</v>
       </c>
-      <c r="O74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="75" spans="1:14">
       <c r="A75" t="s">
         <v>19</v>
       </c>
@@ -7301,38 +6708,41 @@
       <c r="C75" t="s">
         <v>244</v>
       </c>
+      <c r="D75" t="s">
+        <v>390</v>
+      </c>
+      <c r="E75" t="s">
+        <v>484</v>
+      </c>
       <c r="F75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="b">
         <v>0</v>
       </c>
       <c r="H75" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="I75" t="b">
         <v>0</v>
       </c>
       <c r="J75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N75">
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
       <c r="A76" t="s">
         <v>19</v>
       </c>
@@ -7343,10 +6753,10 @@
         <v>245</v>
       </c>
       <c r="D76" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E76" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F76" t="b">
         <v>1</v>
@@ -7355,7 +6765,7 @@
         <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="I76" t="b">
         <v>1</v>
@@ -7375,14 +6785,8 @@
       <c r="N76">
         <v>1</v>
       </c>
-      <c r="O76">
-        <v>0</v>
-      </c>
-      <c r="P76" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="77" spans="1:14">
       <c r="A77" t="s">
         <v>19</v>
       </c>
@@ -7393,10 +6797,10 @@
         <v>246</v>
       </c>
       <c r="D77" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E77" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F77" t="b">
         <v>1</v>
@@ -7405,7 +6809,7 @@
         <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="I77" t="b">
         <v>1</v>
@@ -7425,11 +6829,8 @@
       <c r="N77">
         <v>1</v>
       </c>
-      <c r="O77">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:14">
       <c r="A78" t="s">
         <v>19</v>
       </c>
@@ -7440,10 +6841,10 @@
         <v>247</v>
       </c>
       <c r="D78" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E78" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F78" t="b">
         <v>1</v>
@@ -7452,7 +6853,7 @@
         <v>1</v>
       </c>
       <c r="H78" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="I78" t="b">
         <v>1</v>
@@ -7472,11 +6873,8 @@
       <c r="N78">
         <v>1</v>
       </c>
-      <c r="O78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="1:14">
       <c r="A79" t="s">
         <v>19</v>
       </c>
@@ -7487,10 +6885,10 @@
         <v>248</v>
       </c>
       <c r="D79" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E79" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F79" t="b">
         <v>1</v>
@@ -7499,7 +6897,7 @@
         <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="I79" t="b">
         <v>1</v>
@@ -7519,11 +6917,8 @@
       <c r="N79">
         <v>1</v>
       </c>
-      <c r="O79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:14">
       <c r="A80" t="s">
         <v>20</v>
       </c>
@@ -7534,10 +6929,10 @@
         <v>249</v>
       </c>
       <c r="D80" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E80" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F80" t="b">
         <v>1</v>
@@ -7546,7 +6941,7 @@
         <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="I80" t="b">
         <v>1</v>
@@ -7566,11 +6961,8 @@
       <c r="N80">
         <v>1</v>
       </c>
-      <c r="O80">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="1:14">
       <c r="A81" t="s">
         <v>20</v>
       </c>
@@ -7581,10 +6973,10 @@
         <v>250</v>
       </c>
       <c r="D81" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E81" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F81" t="b">
         <v>1</v>
@@ -7593,7 +6985,7 @@
         <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="I81" t="b">
         <v>1</v>
@@ -7613,11 +7005,8 @@
       <c r="N81">
         <v>1</v>
       </c>
-      <c r="O81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:14">
       <c r="A82" t="s">
         <v>20</v>
       </c>
@@ -7628,10 +7017,10 @@
         <v>251</v>
       </c>
       <c r="D82" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E82" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F82" t="b">
         <v>1</v>
@@ -7640,7 +7029,7 @@
         <v>1</v>
       </c>
       <c r="H82" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="I82" t="b">
         <v>1</v>
@@ -7660,11 +7049,8 @@
       <c r="N82">
         <v>1</v>
       </c>
-      <c r="O82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="83" spans="1:14">
       <c r="A83" t="s">
         <v>20</v>
       </c>
@@ -7675,10 +7061,10 @@
         <v>252</v>
       </c>
       <c r="D83" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E83" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F83" t="b">
         <v>0</v>
@@ -7687,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H83" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="I83" t="b">
         <v>0</v>
@@ -7699,7 +7085,7 @@
         <v>0</v>
       </c>
       <c r="L83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M83">
         <v>0</v>
@@ -7707,11 +7093,8 @@
       <c r="N83">
         <v>0</v>
       </c>
-      <c r="O83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="1:14">
       <c r="A84" t="s">
         <v>20</v>
       </c>
@@ -7722,10 +7105,10 @@
         <v>253</v>
       </c>
       <c r="D84" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E84" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F84" t="b">
         <v>1</v>
@@ -7734,7 +7117,7 @@
         <v>1</v>
       </c>
       <c r="H84" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="I84" t="b">
         <v>1</v>
@@ -7754,11 +7137,8 @@
       <c r="N84">
         <v>1</v>
       </c>
-      <c r="O84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:14">
       <c r="A85" t="s">
         <v>20</v>
       </c>
@@ -7769,10 +7149,10 @@
         <v>254</v>
       </c>
       <c r="D85" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E85" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F85" t="b">
         <v>1</v>
@@ -7781,7 +7161,7 @@
         <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="I85" t="b">
         <v>1</v>
@@ -7801,11 +7181,8 @@
       <c r="N85">
         <v>1</v>
       </c>
-      <c r="O85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="1:14">
       <c r="A86" t="s">
         <v>20</v>
       </c>
@@ -7816,10 +7193,10 @@
         <v>255</v>
       </c>
       <c r="D86" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E86" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F86" t="b">
         <v>1</v>
@@ -7828,7 +7205,7 @@
         <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="I86" t="b">
         <v>1</v>
@@ -7848,11 +7225,8 @@
       <c r="N86">
         <v>1</v>
       </c>
-      <c r="O86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="87" spans="1:14">
       <c r="A87" t="s">
         <v>20</v>
       </c>
@@ -7863,10 +7237,10 @@
         <v>256</v>
       </c>
       <c r="D87" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E87" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F87" t="b">
         <v>1</v>
@@ -7875,7 +7249,7 @@
         <v>1</v>
       </c>
       <c r="H87" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="I87" t="b">
         <v>1</v>
@@ -7895,11 +7269,8 @@
       <c r="N87">
         <v>1</v>
       </c>
-      <c r="O87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="88" spans="1:14">
       <c r="A88" t="s">
         <v>20</v>
       </c>
@@ -7910,10 +7281,10 @@
         <v>257</v>
       </c>
       <c r="D88" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E88" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F88" t="b">
         <v>1</v>
@@ -7922,7 +7293,7 @@
         <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="I88" t="b">
         <v>1</v>
@@ -7942,14 +7313,8 @@
       <c r="N88">
         <v>1</v>
       </c>
-      <c r="O88">
-        <v>0</v>
-      </c>
-      <c r="P88" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="89" spans="1:14">
       <c r="A89" t="s">
         <v>20</v>
       </c>
@@ -7960,10 +7325,10 @@
         <v>258</v>
       </c>
       <c r="D89" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E89" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F89" t="b">
         <v>1</v>
@@ -7972,7 +7337,7 @@
         <v>1</v>
       </c>
       <c r="H89" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="I89" t="b">
         <v>1</v>
@@ -7992,14 +7357,8 @@
       <c r="N89">
         <v>1</v>
       </c>
-      <c r="O89">
-        <v>0</v>
-      </c>
-      <c r="P89" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="1:14">
       <c r="A90" t="s">
         <v>20</v>
       </c>
@@ -8010,43 +7369,40 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E90" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G90" t="b">
         <v>0</v>
       </c>
       <c r="H90" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="I90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J90" t="b">
         <v>0</v>
       </c>
       <c r="K90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L90">
         <v>5</v>
       </c>
       <c r="M90">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N90">
         <v>0</v>
       </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:14">
       <c r="A91" t="s">
         <v>20</v>
       </c>
@@ -8057,10 +7413,10 @@
         <v>260</v>
       </c>
       <c r="D91" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E91" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F91" t="b">
         <v>1</v>
@@ -8069,7 +7425,7 @@
         <v>1</v>
       </c>
       <c r="H91" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="I91" t="b">
         <v>1</v>
@@ -8089,11 +7445,8 @@
       <c r="N91">
         <v>1</v>
       </c>
-      <c r="O91">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:14">
       <c r="A92" t="s">
         <v>20</v>
       </c>
@@ -8104,10 +7457,10 @@
         <v>261</v>
       </c>
       <c r="D92" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E92" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F92" t="b">
         <v>1</v>
@@ -8116,7 +7469,7 @@
         <v>1</v>
       </c>
       <c r="H92" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="I92" t="b">
         <v>1</v>
@@ -8136,14 +7489,8 @@
       <c r="N92">
         <v>1</v>
       </c>
-      <c r="O92">
-        <v>0</v>
-      </c>
-      <c r="P92" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:14">
       <c r="A93" t="s">
         <v>20</v>
       </c>
@@ -8154,10 +7501,10 @@
         <v>262</v>
       </c>
       <c r="D93" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E93" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F93" t="b">
         <v>1</v>
@@ -8166,7 +7513,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="I93" t="b">
         <v>1</v>
@@ -8186,11 +7533,8 @@
       <c r="N93">
         <v>1</v>
       </c>
-      <c r="O93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:14">
       <c r="A94" t="s">
         <v>20</v>
       </c>
@@ -8201,10 +7545,10 @@
         <v>263</v>
       </c>
       <c r="D94" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E94" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F94" t="b">
         <v>1</v>
@@ -8213,7 +7557,7 @@
         <v>1</v>
       </c>
       <c r="H94" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="I94" t="b">
         <v>1</v>
@@ -8233,11 +7577,8 @@
       <c r="N94">
         <v>1</v>
       </c>
-      <c r="O94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="1:14">
       <c r="A95" t="s">
         <v>20</v>
       </c>
@@ -8248,43 +7589,40 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E95" t="s">
-        <v>489</v>
+        <v>465</v>
       </c>
       <c r="F95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="I95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="b">
         <v>0</v>
       </c>
       <c r="K95">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L95">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95">
-        <v>0</v>
-      </c>
-      <c r="O95">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
       <c r="A96" t="s">
         <v>21</v>
       </c>
@@ -8295,10 +7633,10 @@
         <v>265</v>
       </c>
       <c r="D96" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E96" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F96" t="b">
         <v>1</v>
@@ -8307,7 +7645,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="I96" t="b">
         <v>1</v>
@@ -8327,11 +7665,8 @@
       <c r="N96">
         <v>1</v>
       </c>
-      <c r="O96">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="97" spans="1:14">
       <c r="A97" t="s">
         <v>21</v>
       </c>
@@ -8342,10 +7677,10 @@
         <v>266</v>
       </c>
       <c r="D97" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E97" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F97" t="b">
         <v>1</v>
@@ -8354,7 +7689,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="I97" t="b">
         <v>1</v>
@@ -8374,11 +7709,8 @@
       <c r="N97">
         <v>1</v>
       </c>
-      <c r="O97">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="98" spans="1:14">
       <c r="A98" t="s">
         <v>21</v>
       </c>
@@ -8389,43 +7721,40 @@
         <v>267</v>
       </c>
       <c r="D98" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E98" t="s">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="F98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" t="b">
         <v>0</v>
       </c>
       <c r="H98" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="I98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" t="b">
         <v>0</v>
       </c>
       <c r="K98">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L98">
         <v>5</v>
       </c>
       <c r="M98">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="N98">
-        <v>1</v>
-      </c>
-      <c r="O98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
       <c r="A99" t="s">
         <v>21</v>
       </c>
@@ -8436,10 +7765,10 @@
         <v>268</v>
       </c>
       <c r="D99" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E99" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F99" t="b">
         <v>1</v>
@@ -8448,7 +7777,7 @@
         <v>1</v>
       </c>
       <c r="H99" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="I99" t="b">
         <v>1</v>
@@ -8468,11 +7797,8 @@
       <c r="N99">
         <v>1</v>
       </c>
-      <c r="O99">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="100" spans="1:14">
       <c r="A100" t="s">
         <v>21</v>
       </c>
@@ -8483,10 +7809,10 @@
         <v>269</v>
       </c>
       <c r="D100" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E100" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F100" t="b">
         <v>1</v>
@@ -8495,7 +7821,7 @@
         <v>1</v>
       </c>
       <c r="H100" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="I100" t="b">
         <v>1</v>
@@ -8515,11 +7841,8 @@
       <c r="N100">
         <v>1</v>
       </c>
-      <c r="O100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="101" spans="1:14">
       <c r="A101" t="s">
         <v>21</v>
       </c>
@@ -8530,10 +7853,10 @@
         <v>270</v>
       </c>
       <c r="D101" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E101" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F101" t="b">
         <v>1</v>
@@ -8542,7 +7865,7 @@
         <v>1</v>
       </c>
       <c r="H101" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="I101" t="b">
         <v>1</v>
@@ -8562,11 +7885,8 @@
       <c r="N101">
         <v>1</v>
       </c>
-      <c r="O101">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="102" spans="1:14">
       <c r="A102" t="s">
         <v>21</v>
       </c>
@@ -8577,10 +7897,10 @@
         <v>271</v>
       </c>
       <c r="D102" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E102" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F102" t="b">
         <v>1</v>
@@ -8589,7 +7909,7 @@
         <v>1</v>
       </c>
       <c r="H102" t="s">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="I102" t="b">
         <v>1</v>
@@ -8609,11 +7929,8 @@
       <c r="N102">
         <v>1</v>
       </c>
-      <c r="O102">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="103" spans="1:14">
       <c r="A103" t="s">
         <v>21</v>
       </c>
@@ -8624,10 +7941,10 @@
         <v>272</v>
       </c>
       <c r="D103" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E103" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F103" t="b">
         <v>1</v>
@@ -8636,7 +7953,7 @@
         <v>1</v>
       </c>
       <c r="H103" t="s">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="I103" t="b">
         <v>1</v>
@@ -8656,11 +7973,8 @@
       <c r="N103">
         <v>1</v>
       </c>
-      <c r="O103">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="104" spans="1:14">
       <c r="A104" t="s">
         <v>21</v>
       </c>
@@ -8671,10 +7985,10 @@
         <v>273</v>
       </c>
       <c r="D104" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E104" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F104" t="b">
         <v>1</v>
@@ -8683,7 +7997,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="I104" t="b">
         <v>1</v>
@@ -8703,11 +8017,8 @@
       <c r="N104">
         <v>1</v>
       </c>
-      <c r="O104">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="105" spans="1:14">
       <c r="A105" t="s">
         <v>22</v>
       </c>
@@ -8718,10 +8029,10 @@
         <v>274</v>
       </c>
       <c r="D105" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E105" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F105" t="b">
         <v>1</v>
@@ -8730,7 +8041,7 @@
         <v>1</v>
       </c>
       <c r="H105" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="I105" t="b">
         <v>1</v>
@@ -8750,14 +8061,8 @@
       <c r="N105">
         <v>1</v>
       </c>
-      <c r="O105">
-        <v>0</v>
-      </c>
-      <c r="P105" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="106" spans="1:14">
       <c r="A106" t="s">
         <v>22</v>
       </c>
@@ -8768,10 +8073,10 @@
         <v>275</v>
       </c>
       <c r="D106" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E106" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F106" t="b">
         <v>1</v>
@@ -8780,7 +8085,7 @@
         <v>1</v>
       </c>
       <c r="H106" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="I106" t="b">
         <v>1</v>
@@ -8800,14 +8105,8 @@
       <c r="N106">
         <v>1</v>
       </c>
-      <c r="O106">
-        <v>1</v>
-      </c>
-      <c r="P106" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="107" spans="1:14">
       <c r="A107" t="s">
         <v>22</v>
       </c>
@@ -8818,10 +8117,10 @@
         <v>276</v>
       </c>
       <c r="D107" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E107" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F107" t="b">
         <v>1</v>
@@ -8830,7 +8129,7 @@
         <v>1</v>
       </c>
       <c r="H107" t="s">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="I107" t="b">
         <v>1</v>
@@ -8850,14 +8149,8 @@
       <c r="N107">
         <v>1</v>
       </c>
-      <c r="O107">
-        <v>0</v>
-      </c>
-      <c r="P107" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="108" spans="1:14">
       <c r="A108" t="s">
         <v>22</v>
       </c>
@@ -8868,10 +8161,10 @@
         <v>277</v>
       </c>
       <c r="D108" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E108" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F108" t="b">
         <v>1</v>
@@ -8880,7 +8173,7 @@
         <v>1</v>
       </c>
       <c r="H108" t="s">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="I108" t="b">
         <v>1</v>
@@ -8900,14 +8193,8 @@
       <c r="N108">
         <v>1</v>
       </c>
-      <c r="O108">
-        <v>0</v>
-      </c>
-      <c r="P108" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="109" spans="1:14">
       <c r="A109" t="s">
         <v>22</v>
       </c>
@@ -8918,10 +8205,10 @@
         <v>278</v>
       </c>
       <c r="D109" t="s">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="E109" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="F109" t="b">
         <v>0</v>
@@ -8930,7 +8217,7 @@
         <v>0</v>
       </c>
       <c r="H109" t="s">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="I109" t="b">
         <v>0</v>
@@ -8950,11 +8237,8 @@
       <c r="N109">
         <v>0.5</v>
       </c>
-      <c r="O109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="110" spans="1:14">
       <c r="A110" t="s">
         <v>22</v>
       </c>
@@ -8965,10 +8249,10 @@
         <v>279</v>
       </c>
       <c r="D110" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E110" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F110" t="b">
         <v>1</v>
@@ -8977,7 +8261,7 @@
         <v>1</v>
       </c>
       <c r="H110" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="I110" t="b">
         <v>1</v>
@@ -8997,14 +8281,8 @@
       <c r="N110">
         <v>1</v>
       </c>
-      <c r="O110">
-        <v>0</v>
-      </c>
-      <c r="P110" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="111" spans="1:14">
       <c r="A111" t="s">
         <v>22</v>
       </c>
@@ -9015,10 +8293,10 @@
         <v>280</v>
       </c>
       <c r="D111" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E111" t="s">
-        <v>491</v>
+        <v>471</v>
       </c>
       <c r="F111" t="b">
         <v>0</v>
@@ -9027,7 +8305,7 @@
         <v>0</v>
       </c>
       <c r="H111" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="I111" t="b">
         <v>0</v>
@@ -9039,7 +8317,7 @@
         <v>0</v>
       </c>
       <c r="L111">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M111">
         <v>0</v>
@@ -9047,11 +8325,8 @@
       <c r="N111">
         <v>0</v>
       </c>
-      <c r="O111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="112" spans="1:14">
       <c r="A112" t="s">
         <v>22</v>
       </c>
@@ -9062,10 +8337,10 @@
         <v>281</v>
       </c>
       <c r="D112" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E112" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F112" t="b">
         <v>1</v>
@@ -9074,7 +8349,7 @@
         <v>1</v>
       </c>
       <c r="H112" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="I112" t="b">
         <v>1</v>
@@ -9094,11 +8369,8 @@
       <c r="N112">
         <v>1</v>
       </c>
-      <c r="O112">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="113" spans="1:14">
       <c r="A113" t="s">
         <v>22</v>
       </c>
@@ -9109,10 +8381,10 @@
         <v>236</v>
       </c>
       <c r="D113" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E113" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F113" t="b">
         <v>1</v>
@@ -9121,7 +8393,7 @@
         <v>1</v>
       </c>
       <c r="H113" t="s">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="I113" t="b">
         <v>1</v>
@@ -9141,11 +8413,8 @@
       <c r="N113">
         <v>1</v>
       </c>
-      <c r="O113">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="114" spans="1:14">
       <c r="A114" t="s">
         <v>22</v>
       </c>
@@ -9156,10 +8425,10 @@
         <v>238</v>
       </c>
       <c r="D114" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E114" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F114" t="b">
         <v>1</v>
@@ -9168,7 +8437,7 @@
         <v>1</v>
       </c>
       <c r="H114" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="I114" t="b">
         <v>1</v>
@@ -9188,14 +8457,8 @@
       <c r="N114">
         <v>1</v>
       </c>
-      <c r="O114">
-        <v>0</v>
-      </c>
-      <c r="P114" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="115" spans="1:14">
       <c r="A115" t="s">
         <v>22</v>
       </c>
@@ -9206,10 +8469,10 @@
         <v>240</v>
       </c>
       <c r="D115" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E115" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F115" t="b">
         <v>1</v>
@@ -9218,7 +8481,7 @@
         <v>1</v>
       </c>
       <c r="H115" t="s">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="I115" t="b">
         <v>1</v>
@@ -9238,14 +8501,8 @@
       <c r="N115">
         <v>1</v>
       </c>
-      <c r="O115">
-        <v>1</v>
-      </c>
-      <c r="P115" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="116" spans="1:14">
       <c r="A116" t="s">
         <v>22</v>
       </c>
@@ -9256,43 +8513,40 @@
         <v>282</v>
       </c>
       <c r="D116" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E116" t="s">
-        <v>492</v>
+        <v>467</v>
       </c>
       <c r="F116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116" t="s">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="I116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K116">
         <v>7</v>
       </c>
       <c r="L116">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M116">
-        <v>0.63636363636363635</v>
+        <v>1</v>
       </c>
       <c r="N116">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="O116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14">
       <c r="A117" t="s">
         <v>22</v>
       </c>
@@ -9303,10 +8557,10 @@
         <v>283</v>
       </c>
       <c r="D117" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E117" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F117" t="b">
         <v>1</v>
@@ -9315,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="H117" t="s">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="I117" t="b">
         <v>1</v>
@@ -9335,14 +8589,8 @@
       <c r="N117">
         <v>1</v>
       </c>
-      <c r="O117">
-        <v>0</v>
-      </c>
-      <c r="P117" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="118" spans="1:14">
       <c r="A118" t="s">
         <v>22</v>
       </c>
@@ -9353,10 +8601,10 @@
         <v>284</v>
       </c>
       <c r="D118" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E118" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F118" t="b">
         <v>1</v>
@@ -9365,7 +8613,7 @@
         <v>1</v>
       </c>
       <c r="H118" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="I118" t="b">
         <v>1</v>
@@ -9385,11 +8633,8 @@
       <c r="N118">
         <v>1</v>
       </c>
-      <c r="O118">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="119" spans="1:14">
       <c r="A119" t="s">
         <v>22</v>
       </c>
@@ -9400,10 +8645,10 @@
         <v>285</v>
       </c>
       <c r="D119" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E119" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F119" t="b">
         <v>1</v>
@@ -9412,7 +8657,7 @@
         <v>1</v>
       </c>
       <c r="H119" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="I119" t="b">
         <v>1</v>
@@ -9432,14 +8677,8 @@
       <c r="N119">
         <v>1</v>
       </c>
-      <c r="O119">
-        <v>0</v>
-      </c>
-      <c r="P119" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="120" spans="1:14">
       <c r="A120" t="s">
         <v>23</v>
       </c>
@@ -9450,10 +8689,10 @@
         <v>286</v>
       </c>
       <c r="D120" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E120" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F120" t="b">
         <v>1</v>
@@ -9462,7 +8701,7 @@
         <v>1</v>
       </c>
       <c r="H120" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="I120" t="b">
         <v>1</v>
@@ -9482,11 +8721,8 @@
       <c r="N120">
         <v>1</v>
       </c>
-      <c r="O120">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="121" spans="1:14">
       <c r="A121" t="s">
         <v>23</v>
       </c>
@@ -9497,43 +8733,40 @@
         <v>287</v>
       </c>
       <c r="D121" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E121" t="s">
-        <v>493</v>
+        <v>470</v>
       </c>
       <c r="F121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="I121" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" t="b">
         <v>0</v>
       </c>
       <c r="K121">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L121">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N121">
-        <v>0</v>
-      </c>
-      <c r="O121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14">
       <c r="A122" t="s">
         <v>23</v>
       </c>
@@ -9547,7 +8780,7 @@
         <v>319</v>
       </c>
       <c r="E122" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F122" t="b">
         <v>1</v>
@@ -9556,7 +8789,7 @@
         <v>1</v>
       </c>
       <c r="H122" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="I122" t="b">
         <v>1</v>
@@ -9576,11 +8809,8 @@
       <c r="N122">
         <v>1</v>
       </c>
-      <c r="O122">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="123" spans="1:14">
       <c r="A123" t="s">
         <v>23</v>
       </c>
@@ -9591,10 +8821,10 @@
         <v>289</v>
       </c>
       <c r="D123" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E123" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F123" t="b">
         <v>1</v>
@@ -9603,7 +8833,7 @@
         <v>1</v>
       </c>
       <c r="H123" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="I123" t="b">
         <v>1</v>
@@ -9623,11 +8853,8 @@
       <c r="N123">
         <v>1</v>
       </c>
-      <c r="O123">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="124" spans="1:14">
       <c r="A124" t="s">
         <v>23</v>
       </c>
@@ -9638,43 +8865,40 @@
         <v>290</v>
       </c>
       <c r="D124" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E124" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="F124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" t="b">
         <v>0</v>
       </c>
       <c r="H124" t="s">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="I124" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L124">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M124">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="N124">
-        <v>0.2</v>
-      </c>
-      <c r="O124">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14">
       <c r="A125" t="s">
         <v>23</v>
       </c>
@@ -9685,10 +8909,10 @@
         <v>291</v>
       </c>
       <c r="D125" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E125" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F125" t="b">
         <v>1</v>
@@ -9697,7 +8921,7 @@
         <v>1</v>
       </c>
       <c r="H125" t="s">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="I125" t="b">
         <v>1</v>
@@ -9717,11 +8941,8 @@
       <c r="N125">
         <v>1</v>
       </c>
-      <c r="O125">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="126" spans="1:14">
       <c r="A126" t="s">
         <v>23</v>
       </c>
@@ -9732,10 +8953,10 @@
         <v>292</v>
       </c>
       <c r="D126" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E126" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F126" t="b">
         <v>1</v>
@@ -9744,7 +8965,7 @@
         <v>1</v>
       </c>
       <c r="H126" t="s">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="I126" t="b">
         <v>1</v>
@@ -9764,11 +8985,8 @@
       <c r="N126">
         <v>1</v>
       </c>
-      <c r="O126">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="127" spans="1:14">
       <c r="A127" t="s">
         <v>23</v>
       </c>
@@ -9779,10 +8997,10 @@
         <v>293</v>
       </c>
       <c r="D127" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E127" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F127" t="b">
         <v>1</v>
@@ -9791,7 +9009,7 @@
         <v>1</v>
       </c>
       <c r="H127" t="s">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="I127" t="b">
         <v>1</v>
@@ -9811,11 +9029,8 @@
       <c r="N127">
         <v>1</v>
       </c>
-      <c r="O127">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="128" spans="1:14">
       <c r="A128" t="s">
         <v>23</v>
       </c>
@@ -9826,10 +9041,10 @@
         <v>294</v>
       </c>
       <c r="D128" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E128" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F128" t="b">
         <v>1</v>
@@ -9838,7 +9053,7 @@
         <v>1</v>
       </c>
       <c r="H128" t="s">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="I128" t="b">
         <v>1</v>
@@ -9858,11 +9073,8 @@
       <c r="N128">
         <v>1</v>
       </c>
-      <c r="O128">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="129" spans="1:14">
       <c r="A129" t="s">
         <v>24</v>
       </c>
@@ -9873,10 +9085,10 @@
         <v>295</v>
       </c>
       <c r="D129" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E129" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F129" t="b">
         <v>1</v>
@@ -9885,7 +9097,7 @@
         <v>1</v>
       </c>
       <c r="H129" t="s">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="I129" t="b">
         <v>1</v>
@@ -9905,11 +9117,8 @@
       <c r="N129">
         <v>1</v>
       </c>
-      <c r="O129">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="130" spans="1:14">
       <c r="A130" t="s">
         <v>24</v>
       </c>
@@ -9920,10 +9129,10 @@
         <v>296</v>
       </c>
       <c r="D130" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E130" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F130" t="b">
         <v>1</v>
@@ -9932,7 +9141,7 @@
         <v>1</v>
       </c>
       <c r="H130" t="s">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="I130" t="b">
         <v>1</v>
@@ -9952,11 +9161,8 @@
       <c r="N130">
         <v>1</v>
       </c>
-      <c r="O130">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="131" spans="1:14">
       <c r="A131" t="s">
         <v>24</v>
       </c>
@@ -9967,10 +9173,10 @@
         <v>297</v>
       </c>
       <c r="D131" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E131" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F131" t="b">
         <v>1</v>
@@ -9979,7 +9185,7 @@
         <v>1</v>
       </c>
       <c r="H131" t="s">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="I131" t="b">
         <v>1</v>
@@ -9999,11 +9205,8 @@
       <c r="N131">
         <v>1</v>
       </c>
-      <c r="O131">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="132" spans="1:14">
       <c r="A132" t="s">
         <v>24</v>
       </c>
@@ -10014,19 +9217,19 @@
         <v>298</v>
       </c>
       <c r="D132" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E132" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="F132" t="b">
         <v>1</v>
       </c>
       <c r="G132" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H132" t="s">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="I132" t="b">
         <v>1</v>
@@ -10035,10 +9238,10 @@
         <v>0</v>
       </c>
       <c r="K132">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L132">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M132">
         <v>1</v>
@@ -10046,11 +9249,8 @@
       <c r="N132">
         <v>1</v>
       </c>
-      <c r="O132">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="133" spans="1:14">
       <c r="A133" t="s">
         <v>24</v>
       </c>
@@ -10061,10 +9261,10 @@
         <v>299</v>
       </c>
       <c r="D133" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E133" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F133" t="b">
         <v>1</v>
@@ -10073,7 +9273,7 @@
         <v>1</v>
       </c>
       <c r="H133" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="I133" t="b">
         <v>1</v>
@@ -10093,11 +9293,8 @@
       <c r="N133">
         <v>1</v>
       </c>
-      <c r="O133">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="134" spans="1:14">
       <c r="A134" t="s">
         <v>24</v>
       </c>
@@ -10108,43 +9305,40 @@
         <v>300</v>
       </c>
       <c r="D134" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E134" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="F134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134" t="b">
         <v>0</v>
       </c>
       <c r="H134" t="s">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="I134" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J134" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K134">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L134">
         <v>8</v>
       </c>
       <c r="M134">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
       <c r="N134">
         <v>0</v>
       </c>
-      <c r="O134">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="135" spans="1:14">
       <c r="A135" t="s">
         <v>24</v>
       </c>
@@ -10155,10 +9349,10 @@
         <v>301</v>
       </c>
       <c r="D135" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E135" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F135" t="b">
         <v>1</v>
@@ -10167,7 +9361,7 @@
         <v>1</v>
       </c>
       <c r="H135" t="s">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="I135" t="b">
         <v>1</v>
@@ -10187,11 +9381,8 @@
       <c r="N135">
         <v>1</v>
       </c>
-      <c r="O135">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="136" spans="1:14">
       <c r="A136" t="s">
         <v>24</v>
       </c>
@@ -10202,10 +9393,10 @@
         <v>302</v>
       </c>
       <c r="D136" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E136" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F136" t="b">
         <v>1</v>
@@ -10214,7 +9405,7 @@
         <v>1</v>
       </c>
       <c r="H136" t="s">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="I136" t="b">
         <v>1</v>
@@ -10234,11 +9425,8 @@
       <c r="N136">
         <v>1</v>
       </c>
-      <c r="O136">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="137" spans="1:14">
       <c r="A137" t="s">
         <v>24</v>
       </c>
@@ -10249,10 +9437,10 @@
         <v>303</v>
       </c>
       <c r="D137" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E137" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F137" t="b">
         <v>1</v>
@@ -10261,7 +9449,7 @@
         <v>1</v>
       </c>
       <c r="H137" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="I137" t="b">
         <v>1</v>
@@ -10281,11 +9469,8 @@
       <c r="N137">
         <v>1</v>
       </c>
-      <c r="O137">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="138" spans="1:14">
       <c r="A138" t="s">
         <v>24</v>
       </c>
@@ -10296,10 +9481,10 @@
         <v>304</v>
       </c>
       <c r="D138" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E138" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F138" t="b">
         <v>1</v>
@@ -10308,7 +9493,7 @@
         <v>1</v>
       </c>
       <c r="H138" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="I138" t="b">
         <v>1</v>
@@ -10328,11 +9513,8 @@
       <c r="N138">
         <v>1</v>
       </c>
-      <c r="O138">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="139" spans="1:14">
       <c r="A139" t="s">
         <v>24</v>
       </c>
@@ -10343,19 +9525,19 @@
         <v>305</v>
       </c>
       <c r="D139" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E139" t="s">
-        <v>496</v>
+        <v>466</v>
       </c>
       <c r="F139" t="b">
         <v>1</v>
       </c>
       <c r="G139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H139" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="I139" t="b">
         <v>1</v>
@@ -10367,22 +9549,16 @@
         <v>8</v>
       </c>
       <c r="L139">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M139">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14">
       <c r="A140" t="s">
         <v>24</v>
       </c>
@@ -10393,10 +9569,10 @@
         <v>306</v>
       </c>
       <c r="D140" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E140" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F140" t="b">
         <v>1</v>
@@ -10405,7 +9581,7 @@
         <v>1</v>
       </c>
       <c r="H140" t="s">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="I140" t="b">
         <v>1</v>
@@ -10425,14 +9601,8 @@
       <c r="N140">
         <v>1</v>
       </c>
-      <c r="O140">
-        <v>0</v>
-      </c>
-      <c r="P140" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="141" spans="1:14">
       <c r="A141" t="s">
         <v>24</v>
       </c>
@@ -10443,10 +9613,10 @@
         <v>307</v>
       </c>
       <c r="D141" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E141" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="F141" t="b">
         <v>1</v>
@@ -10455,7 +9625,7 @@
         <v>1</v>
       </c>
       <c r="H141" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="I141" t="b">
         <v>1</v>
@@ -10475,11 +9645,8 @@
       <c r="N141">
         <v>1</v>
       </c>
-      <c r="O141">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="142" spans="1:14">
       <c r="A142" t="s">
         <v>24</v>
       </c>
@@ -10490,10 +9657,10 @@
         <v>308</v>
       </c>
       <c r="D142" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E142" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F142" t="b">
         <v>1</v>
@@ -10502,7 +9669,7 @@
         <v>1</v>
       </c>
       <c r="H142" t="s">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="I142" t="b">
         <v>1</v>
@@ -10522,11 +9689,8 @@
       <c r="N142">
         <v>1</v>
       </c>
-      <c r="O142">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="143" spans="1:14">
       <c r="A143" t="s">
         <v>25</v>
       </c>
@@ -10537,10 +9701,10 @@
         <v>309</v>
       </c>
       <c r="D143" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E143" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F143" t="b">
         <v>1</v>
@@ -10549,7 +9713,7 @@
         <v>1</v>
       </c>
       <c r="H143" t="s">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="I143" t="b">
         <v>1</v>
@@ -10569,11 +9733,8 @@
       <c r="N143">
         <v>1</v>
       </c>
-      <c r="O143">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="144" spans="1:14">
       <c r="A144" t="s">
         <v>25</v>
       </c>
@@ -10584,10 +9745,10 @@
         <v>310</v>
       </c>
       <c r="D144" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E144" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F144" t="b">
         <v>1</v>
@@ -10596,7 +9757,7 @@
         <v>1</v>
       </c>
       <c r="H144" t="s">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="I144" t="b">
         <v>1</v>
@@ -10616,14 +9777,8 @@
       <c r="N144">
         <v>1</v>
       </c>
-      <c r="O144">
-        <v>0</v>
-      </c>
-      <c r="P144" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="145" spans="1:14">
       <c r="A145" t="s">
         <v>25</v>
       </c>
@@ -10634,10 +9789,10 @@
         <v>311</v>
       </c>
       <c r="D145" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E145" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F145" t="b">
         <v>1</v>
@@ -10646,7 +9801,7 @@
         <v>1</v>
       </c>
       <c r="H145" t="s">
-        <v>633</v>
+        <v>625</v>
       </c>
       <c r="I145" t="b">
         <v>1</v>
@@ -10666,14 +9821,8 @@
       <c r="N145">
         <v>1</v>
       </c>
-      <c r="O145">
-        <v>0</v>
-      </c>
-      <c r="P145" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="146" spans="1:14">
       <c r="A146" t="s">
         <v>25</v>
       </c>
@@ -10687,7 +9836,7 @@
         <v>361</v>
       </c>
       <c r="E146" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F146" t="b">
         <v>1</v>
@@ -10696,7 +9845,7 @@
         <v>1</v>
       </c>
       <c r="H146" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="I146" t="b">
         <v>1</v>
@@ -10716,11 +9865,8 @@
       <c r="N146">
         <v>1</v>
       </c>
-      <c r="O146">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="147" spans="1:14">
       <c r="A147" t="s">
         <v>25</v>
       </c>
@@ -10731,43 +9877,40 @@
         <v>313</v>
       </c>
       <c r="D147" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E147" t="s">
-        <v>497</v>
+        <v>481</v>
       </c>
       <c r="F147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147" t="b">
         <v>0</v>
       </c>
       <c r="H147" t="s">
-        <v>634</v>
+        <v>626</v>
       </c>
       <c r="I147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L147">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M147">
-        <v>0.83333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="N147">
         <v>0.5</v>
       </c>
-      <c r="O147">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="148" spans="1:14">
       <c r="A148" t="s">
         <v>25</v>
       </c>
@@ -10778,10 +9921,10 @@
         <v>314</v>
       </c>
       <c r="D148" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E148" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F148" t="b">
         <v>1</v>
@@ -10790,7 +9933,7 @@
         <v>1</v>
       </c>
       <c r="H148" t="s">
-        <v>635</v>
+        <v>627</v>
       </c>
       <c r="I148" t="b">
         <v>1</v>
@@ -10810,11 +9953,8 @@
       <c r="N148">
         <v>1</v>
       </c>
-      <c r="O148">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="149" spans="1:14">
       <c r="A149" t="s">
         <v>25</v>
       </c>
@@ -10825,10 +9965,10 @@
         <v>315</v>
       </c>
       <c r="D149" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E149" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F149" t="b">
         <v>1</v>
@@ -10837,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="H149" t="s">
-        <v>636</v>
+        <v>628</v>
       </c>
       <c r="I149" t="b">
         <v>1</v>
@@ -10857,11 +9997,8 @@
       <c r="N149">
         <v>1</v>
       </c>
-      <c r="O149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="150" spans="1:14">
       <c r="A150" t="s">
         <v>25</v>
       </c>
@@ -10872,10 +10009,10 @@
         <v>316</v>
       </c>
       <c r="D150" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E150" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F150" t="b">
         <v>1</v>
@@ -10884,7 +10021,7 @@
         <v>1</v>
       </c>
       <c r="H150" t="s">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="I150" t="b">
         <v>1</v>
@@ -10904,11 +10041,8 @@
       <c r="N150">
         <v>1</v>
       </c>
-      <c r="O150">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="151" spans="1:14">
       <c r="A151" t="s">
         <v>25</v>
       </c>
@@ -10919,10 +10053,10 @@
         <v>317</v>
       </c>
       <c r="D151" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E151" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F151" t="b">
         <v>1</v>
@@ -10931,7 +10065,7 @@
         <v>1</v>
       </c>
       <c r="H151" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="I151" t="b">
         <v>1</v>
@@ -10949,9 +10083,6 @@
         <v>1</v>
       </c>
       <c r="N151">
-        <v>1</v>
-      </c>
-      <c r="O151">
         <v>1</v>
       </c>
     </row>
